--- a/WB_Analytics_Реестр_задач.xlsx
+++ b/WB_Analytics_Реестр_задач.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Реестр задач" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'Реестр задач'!$A$1:$I$124</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'Реестр задач'!$A$1:$I$144</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I124"/>
+  <dimension ref="A1:I144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" max="1" min="1" width="6"/>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Исправлено, не закоммичено (2026-07-02)</t>
+          <t>Исправлено и закоммичено (2026-07-02, commit b3642c5)</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5633,12 +5633,12 @@
       </c>
       <c r="F114" s="7" t="inlineStr">
         <is>
-          <t>Требует решения пользователя</t>
+          <t>Решено — принято. Заменено формальным ТЗ (см. раздел «Редизайн — Steep»)</t>
         </is>
       </c>
       <c r="G114" s="7" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="H114" s="7" t="inlineStr">
@@ -6102,8 +6102,908 @@
         </is>
       </c>
     </row>
+    <row r="125">
+      <c r="A125" s="7" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" s="7" t="inlineStr">
+        <is>
+          <t>Идея</t>
+        </is>
+      </c>
+      <c r="C125" s="7" t="inlineStr">
+        <is>
+          <t>Регистрация / Авторизация</t>
+        </is>
+      </c>
+      <c r="D125" s="7" t="inlineStr">
+        <is>
+          <t>Регистрация</t>
+        </is>
+      </c>
+      <c r="E125" s="7" t="inlineStr">
+        <is>
+          <t>Публичная самостоятельная регистрация пользователей в приложении. Сейчас доступ только через инвайты (см. ролевую модель thoughts/shared/specs/2026-06-25-user-roles.md) — self-signup отсутствует. Требует уточнения: кто может регистрироваться (новые магазины/SaaS-клиенты?), какие поля, нужна ли модерация.</t>
+        </is>
+      </c>
+      <c r="F125" s="7" t="inlineStr">
+        <is>
+          <t>Требует уточнения</t>
+        </is>
+      </c>
+      <c r="G125" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H125" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I125" s="7" t="inlineStr">
+        <is>
+          <t>Пользователь, 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="7" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" s="7" t="inlineStr">
+        <is>
+          <t>Идея</t>
+        </is>
+      </c>
+      <c r="C126" s="7" t="inlineStr">
+        <is>
+          <t>Регистрация / Авторизация</t>
+        </is>
+      </c>
+      <c r="D126" s="7" t="inlineStr">
+        <is>
+          <t>Авторизация</t>
+        </is>
+      </c>
+      <c r="E126" s="7" t="inlineStr">
+        <is>
+          <t>Вход в систему для зарегистрированных пользователей. Уточнить: это доработка существующего better-auth логина или отдельный флоу в рамках новой регистрации.</t>
+        </is>
+      </c>
+      <c r="F126" s="7" t="inlineStr">
+        <is>
+          <t>Требует уточнения</t>
+        </is>
+      </c>
+      <c r="G126" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H126" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I126" s="7" t="inlineStr">
+        <is>
+          <t>Пользователь, 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="7" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" s="7" t="inlineStr">
+        <is>
+          <t>Идея</t>
+        </is>
+      </c>
+      <c r="C127" s="7" t="inlineStr">
+        <is>
+          <t>Регистрация / Авторизация</t>
+        </is>
+      </c>
+      <c r="D127" s="7" t="inlineStr">
+        <is>
+          <t>Оферта</t>
+        </is>
+      </c>
+      <c r="E127" s="7" t="inlineStr">
+        <is>
+          <t>Согласие с офертой/пользовательским соглашением при регистрации (чекбокс + текст документа). Нужен текст оферты и место его хранения/версионирования.</t>
+        </is>
+      </c>
+      <c r="F127" s="7" t="inlineStr">
+        <is>
+          <t>Требует уточнения</t>
+        </is>
+      </c>
+      <c r="G127" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H127" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I127" s="7" t="inlineStr">
+        <is>
+          <t>Пользователь, 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="7" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" s="7" t="inlineStr">
+        <is>
+          <t>Идея</t>
+        </is>
+      </c>
+      <c r="C128" s="7" t="inlineStr">
+        <is>
+          <t>Регистрация / Авторизация</t>
+        </is>
+      </c>
+      <c r="D128" s="7" t="inlineStr">
+        <is>
+          <t>Поддержка зарубежных email</t>
+        </is>
+      </c>
+      <c r="E128" s="7" t="inlineStr">
+        <is>
+          <t>Регистрация/уведомления должны корректно работать с email на зарубежных доменах. Уточнить конкретную проблему: валидация формата, доставка писем (SMTP-провайдер), кириллица в адресе и т.п.</t>
+        </is>
+      </c>
+      <c r="F128" s="7" t="inlineStr">
+        <is>
+          <t>Требует уточнения</t>
+        </is>
+      </c>
+      <c r="G128" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H128" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I128" s="7" t="inlineStr">
+        <is>
+          <t>Пользователь, 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="7" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" s="7" t="inlineStr">
+        <is>
+          <t>Идея</t>
+        </is>
+      </c>
+      <c r="C129" s="7" t="inlineStr">
+        <is>
+          <t>Регистрация / Авторизация</t>
+        </is>
+      </c>
+      <c r="D129" s="7" t="inlineStr">
+        <is>
+          <t>Восстановление пароля</t>
+        </is>
+      </c>
+      <c r="E129" s="7" t="inlineStr">
+        <is>
+          <t>Флоу сброса/восстановления пароля для пользователя. better-auth поддерживает reset-password из коробки — уточнить нужна ли кастомизация (свой email-шаблон, страница) или используем стандартный.</t>
+        </is>
+      </c>
+      <c r="F129" s="7" t="inlineStr">
+        <is>
+          <t>Требует уточнения</t>
+        </is>
+      </c>
+      <c r="G129" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H129" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I129" s="7" t="inlineStr">
+        <is>
+          <t>Пользователь, 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="7" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" s="7" t="inlineStr">
+        <is>
+          <t>Идея</t>
+        </is>
+      </c>
+      <c r="C130" s="7" t="inlineStr">
+        <is>
+          <t>Регистрация / Авторизация</t>
+        </is>
+      </c>
+      <c r="D130" s="7" t="inlineStr">
+        <is>
+          <t>Уведомления в почту/Telegram</t>
+        </is>
+      </c>
+      <c r="E130" s="7" t="inlineStr">
+        <is>
+          <t>Транзакционные уведомления пользователю по email и/или Telegram (например: подтверждение регистрации, смена пароля). Пересекается с Н-1 (Telegram-уведомления), но там речь о бизнес-алертах (спад заказов и т.п.), а здесь — про аккаунт/безопасность. Уточнить состав событий.</t>
+        </is>
+      </c>
+      <c r="F130" s="7" t="inlineStr">
+        <is>
+          <t>Требует уточнения</t>
+        </is>
+      </c>
+      <c r="G130" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H130" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I130" s="7" t="inlineStr">
+        <is>
+          <t>Пользователь, 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="4" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t>Задача</t>
+        </is>
+      </c>
+      <c r="C131" s="4" t="inlineStr">
+        <is>
+          <t>Редизайн — Steep</t>
+        </is>
+      </c>
+      <c r="D131" s="4" t="inlineStr">
+        <is>
+          <t>Редизайн — перенос дизайн-системы Steep на WB Analytics (эпик)</t>
+        </is>
+      </c>
+      <c r="E131" s="4" t="inlineStr">
+        <is>
+          <t>Цель: любой экран отвечает «всё ок или проблема» за 5 секунд, затем даёт разобрать детали без потери контекста. Внедрить светлую редакционную дизайн-систему Steep (Source Serif 4 для заголовков/цифр + Hanken Grotesk для UI, акцент rust #5D2A1A + тёплый/холодный wash, радиус карточек 24px) в Next.js App Router + Tailwind v4 + shadcn — токены слоем --app-* поверх текущей OKLCH-темы, ничего не ломая. Консолидация ~20 текущих страниц src/app/(app)/* в 5 смысловых разделов: Обзор, Финансы, Продажи, Товары, Реклама (роутинг/queries не переписываем — меняем композицию и представление). Обязательные элементы: sticky строка глобального статуса, герой-вердикт раздела, строка-светофор (4 карточки-сигнала), граф взаимосвязей метрик (metricGraph.ts, клик по узлу → зависимости → переход в раздел), единая система пиктограмм picto.tsx, 5 канонических диаграмм (Пульс, Каскад прибыли, Радар выкупа, Запас хода, ABC-вклад) переиспользуемых между разделами. DoD: слой-вердикт выше линии сгиба на каждом разделе; текст в данных ≥13px, герой-цифры 34-52px; ≥1 из 5 канонических диаграмм на разделе; граф связей работает; picto применены everywhere; цвет только как статус-пунктуация (rust + семантика роста/риска); адаптив десктоп/планшет (≥768px). Вне рамок: схема БД и синк (lib/sync*.ts, wb-api.ts), новые метрики/бизнес-расчёты, ролевая модель (используется как есть), мобильная версия &lt;768px. Заменяет собой Н-6 «Новый дизайн» (Q4 2026) — это теперь конкретный формальный ТЗ вместо общей идеи. Эта запись — эпик, реализация разбита по этапам Ф0-Ф5 ниже.</t>
+        </is>
+      </c>
+      <c r="F131" s="4" t="inlineStr">
+        <is>
+          <t>Готово (2026-07-02) — все 6 под-фаз Ф0-Ф5 завершены</t>
+        </is>
+      </c>
+      <c r="G131" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H131" s="4" t="inlineStr">
+        <is>
+          <t>Высокий</t>
+        </is>
+      </c>
+      <c r="I131" s="4" t="inlineStr">
+        <is>
+          <t>ТЗ - перенос дизайна.dc.html, Единая страница - Steep.dc.html, DESIGN (2).md (файлы пользователя, 02.07.2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="4" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" s="4" t="inlineStr">
+        <is>
+          <t>Задача</t>
+        </is>
+      </c>
+      <c r="C132" s="4" t="inlineStr">
+        <is>
+          <t>Редизайн — Steep</t>
+        </is>
+      </c>
+      <c r="D132" s="4" t="inlineStr">
+        <is>
+          <t>Ф0 — Токены дизайн-системы</t>
+        </is>
+      </c>
+      <c r="E132" s="4" t="inlineStr">
+        <is>
+          <t>Токены палитры/типографики в globals.css (слой --app-*, OKLCH), подключение шрифтов Source Serif 4 + Hanken Grotesk в layout.tsx, аудит существующего picto.tsx на полноту иконок. | ИТОГ: добавлен слой --app-* в globals.css (цвет/типографика/формы/отступы, --wb-* не тронуты), подключены Source Serif 4 + Hanken Grotesk (кириллица) через next/font/google в layout.tsx — пока не применены ни к одному компоненту. Аудит picto.tsx: 22 иконки уже monochrome/stroke/currentColor/18×18, для 5 новых разделов иконки уже есть, новых не требуется. Проверено: скриншот дашборда до/после идентичен, консоль без ошибок, Tailwind-стили применяются штатно.</t>
+        </is>
+      </c>
+      <c r="F132" s="4" t="inlineStr">
+        <is>
+          <t>Готово (2026-07-02)</t>
+        </is>
+      </c>
+      <c r="G132" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H132" s="4" t="inlineStr">
+        <is>
+          <t>Высокий</t>
+        </is>
+      </c>
+      <c r="I132" s="4" t="inlineStr">
+        <is>
+          <t>ТЗ - перенос дизайна.dc.html, Единая страница - Steep.dc.html, DESIGN (2).md (файлы пользователя, 02.07.2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="4" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
+          <t>Задача</t>
+        </is>
+      </c>
+      <c r="C133" s="4" t="inlineStr">
+        <is>
+          <t>Редизайн — Steep</t>
+        </is>
+      </c>
+      <c r="D133" s="4" t="inlineStr">
+        <is>
+          <t>Ф1 — SectionShell + sticky статус</t>
+        </is>
+      </c>
+      <c r="E133" s="4" t="inlineStr">
+        <is>
+          <t>Компонент &lt;SectionShell&gt; (рейл + sticky глобальный статус + контейнер раздела). Единый период (год/90д/30д) хранится в URL-параметре и переживает переходы между разделами. | ИТОГ: usePeriod (URL from/to/preset), GlobalStatusBar (sticky, реальные данные), SectionShell (контейнер + слот статуса, rail отложен до Ф4). Объединено с Ф2 по запросу пользователя.</t>
+        </is>
+      </c>
+      <c r="F133" s="4" t="inlineStr">
+        <is>
+          <t>Готово (2026-07-02)</t>
+        </is>
+      </c>
+      <c r="G133" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H133" s="4" t="inlineStr">
+        <is>
+          <t>Высокий</t>
+        </is>
+      </c>
+      <c r="I133" s="4" t="inlineStr">
+        <is>
+          <t>ТЗ - перенос дизайна.dc.html, Единая страница - Steep.dc.html, DESIGN (2).md (файлы пользователя, 02.07.2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="4" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" s="4" t="inlineStr">
+        <is>
+          <t>Задача</t>
+        </is>
+      </c>
+      <c r="C134" s="4" t="inlineStr">
+        <is>
+          <t>Редизайн — Steep</t>
+        </is>
+      </c>
+      <c r="D134" s="4" t="inlineStr">
+        <is>
+          <t>Ф2 — Раздел «Обзор»: вердикт + светофор + 5 диаграмм</t>
+        </is>
+      </c>
+      <c r="E134" s="4" t="inlineStr">
+        <is>
+          <t>&lt;VerdictBand&gt; (герой-вердикт + цифра 34-52px + дельта), &lt;SignalCard&gt; ×4 (Продажи/Запасы/Реклама/Финансы), 5 диаграмм (&lt;ChartCard&gt; + Pulse/Waterfall/BuyoutGauge/RunwayBars/AbcRibbon) на реальных данных queries-overview.ts. | ИТОГ: НЕ строил на /overview (была мёртвая заглушка-redirect) — вместо этого рестайлил /dashboard в Steep, т.к. там уже была рабочая инфраструктура (StatusBanner/SignalCards/HeroKpiStrip/ProfitWaterfall на реальных данных из queries-overview.ts), старые компоненты удалены как неиспользуемые. Добавлены VerdictBand, 4×SignalCard, ChartCard + 5 диаграмм (Pulse/Waterfall/BuyoutGauge/RunwayBars/AbcRibbon — новая лёгкая ABC-агрегация getAbcRevenueShares в queries-overview.ts). Проверено на реальных данных в браузере, tsc чист, найдены и исправлены 2 бага по пути (даты Пульса, двойная ось Y).</t>
+        </is>
+      </c>
+      <c r="F134" s="4" t="inlineStr">
+        <is>
+          <t>Готово (2026-07-02)</t>
+        </is>
+      </c>
+      <c r="G134" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H134" s="4" t="inlineStr">
+        <is>
+          <t>Высокий</t>
+        </is>
+      </c>
+      <c r="I134" s="4" t="inlineStr">
+        <is>
+          <t>ТЗ - перенос дизайна.dc.html, Единая страница - Steep.dc.html, DESIGN (2).md (файлы пользователя, 02.07.2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="4" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" s="4" t="inlineStr">
+        <is>
+          <t>Задача</t>
+        </is>
+      </c>
+      <c r="C135" s="4" t="inlineStr">
+        <is>
+          <t>Редизайн — Steep</t>
+        </is>
+      </c>
+      <c r="D135" s="4" t="inlineStr">
+        <is>
+          <t>Ф3 — Граф связей метрик</t>
+        </is>
+      </c>
+      <c r="E135" s="4" t="inlineStr">
+        <is>
+          <t>lib/metricGraph.ts — карта зависимостей метрик (dependsOn/affects/section) как данные, не хардкод в разметке. Компонент &lt;MetricGraph&gt;: клик по узлу подсвечивает зависимые, панель разбора справа с переходом в раздел (router push с сохранением периода). | ИТОГ: lib/metricGraph.ts (статичная карта depends/affects по 7 метрикам) + компонент MetricGraph (клик→подсветка связей→панель разбора→переход в раздел с сохранением периода), встроен в /dashboard под диаграммами. Проверено интерактивно в браузере.</t>
+        </is>
+      </c>
+      <c r="F135" s="4" t="inlineStr">
+        <is>
+          <t>Готово (2026-07-02)</t>
+        </is>
+      </c>
+      <c r="G135" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H135" s="4" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="I135" s="4" t="inlineStr">
+        <is>
+          <t>ТЗ - перенос дизайна.dc.html, Единая страница - Steep.dc.html, DESIGN (2).md (файлы пользователя, 02.07.2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="4" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" s="4" t="inlineStr">
+        <is>
+          <t>Задача</t>
+        </is>
+      </c>
+      <c r="C136" s="4" t="inlineStr">
+        <is>
+          <t>Редизайн — Steep</t>
+        </is>
+      </c>
+      <c r="D136" s="4" t="inlineStr">
+        <is>
+          <t>Ф4 — Разделы Финансы/Продажи/Товары/Реклама</t>
+        </is>
+      </c>
+      <c r="E136" s="4" t="inlineStr">
+        <is>
+          <t>Тот же шаблон (SectionShell + вердикт + диаграммы), что и Обзор, применить к 4 оставшимся разделам; вложить туда текущие страницы (pnl/costs/cashflow/unit-economics/fin-reports → Финансы; returns/sales-plan/weekly → Продажи; abc/products/sku/storage/supplies/rnp/matrix → Товары; advertising → Реклама). | ИТОГ: архитектурный рефакторинг — GlobalStatusBar перенесён на уровень (app)/layout.tsx (один фетч, фикс. 30 дней, виден теперь ВЕЗДЕ, не только на Обзоре). SectionShell получил maxWidth prop. Применено визуальное оформление Steep (eyebrow+serif заголовок, pill-период) к /pnl, /funnel, /abc, /advertising — внутренняя логика/таблицы/графики НЕ трогал. НЕ делал: полную консолидацию ~20 страниц в 5 разделов с рейлом-вкладками и переделку сайдбара — сознательно вынесено в отдельную задачу (см. следующую строку) как отдельное решение по навигации/IA с более высоким риском.</t>
+        </is>
+      </c>
+      <c r="F136" s="4" t="inlineStr">
+        <is>
+          <t>Готово в облегчённом объёме (2026-07-02)</t>
+        </is>
+      </c>
+      <c r="G136" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H136" s="4" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="I136" s="4" t="inlineStr">
+        <is>
+          <t>ТЗ - перенос дизайна.dc.html, Единая страница - Steep.dc.html, DESIGN (2).md (файлы пользователя, 02.07.2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="4" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t>Задача</t>
+        </is>
+      </c>
+      <c r="C137" s="4" t="inlineStr">
+        <is>
+          <t>Редизайн — Steep</t>
+        </is>
+      </c>
+      <c r="D137" s="4" t="inlineStr">
+        <is>
+          <t>Ф5 — Тёмный режим</t>
+        </is>
+      </c>
+      <c r="E137" s="4" t="inlineStr">
+        <is>
+          <t>Тёмная тема (вариант «1a Светофор» из референсов) через существующий .dark-вариант Tailwind. | ИТОГ: развёл роль --app-ink на --app-text (флипающийся текст) и --app-cta-bg/--app-cta-text (нефлипающаяся контрастная пара для кнопок/активных пилюль/акцентных баров) — иначе кнопки становились белыми с белым текстом при простой инверсии. Добавлен .dark блок в globals.css со всеми --app-* токенами. Переключатель темы в сайдбаре + localStorage("wb-theme") + anti-FOUC inline-script в layout.tsx. РЕАЛЬНЫЙ БАГ по пути: React гидратация перезаписывала className &lt;html&gt; и стирала класс dark, выставленный anti-FOUC скриптом (~84мс после), несмотря на suppressHydrationWarning — исправлено доп. useEffect-переприменением класса в Sidebar. Существующие shadcn/legacy-компоненты (Card и т.д.) корректно потемнели бесплатно — они уже использовали tailwind .dark-вариант. Проверено на /dashboard, /pnl, /abc: переключение туда-обратно, persist через reload.</t>
+        </is>
+      </c>
+      <c r="F137" s="4" t="inlineStr">
+        <is>
+          <t>Готово (2026-07-02)</t>
+        </is>
+      </c>
+      <c r="G137" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H137" s="4" t="inlineStr">
+        <is>
+          <t>Низкий</t>
+        </is>
+      </c>
+      <c r="I137" s="4" t="inlineStr">
+        <is>
+          <t>ТЗ - перенос дизайна.dc.html, Единая страница - Steep.dc.html, DESIGN (2).md (файлы пользователя, 02.07.2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>Баг</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Баги</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Дашборд падает при пустых данных (d.tasks.length)</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>src/app/(app)/dashboard/page.tsx:154 — TypeError: Cannot read properties of undefined (reading 'length') при чтении d.tasks.length. Воспроизведено на новом пользователе без истории данных (гонка: компонент рендерится раньше, чем ответит API, либо часть полей d не имеет дефолта). Нужен фолбэк d.tasks ?? [] (и вероятно похожие места в этом компоненте). | ИТОГ: исправлено попутно при переписывании dashboard/page.tsx под Ф2 — добавлен fallback tasks ?? [] и проверка r.ok в fetch.</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>Исправлено (2026-07-02)</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>Обнаружено при тестировании Ф0 редизайна, сессия 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>Баг</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>Баги</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Дашборд не скрывает прибыль/маржу от ad_manager</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>Ни /dashboard, ни его компоненты нигде не проверяют роль (нет requireRole/CAN_VIEW_PNL), хотя по ROADMAP (П-9 UI-ограничения) прибыль/себестоимость должны быть скрыты для ad_manager/viewer, как в /pnl и /unit-economics. Обнаружено при редизайне Ф2, не исправлено — вне рамок задачи (ТЗ явно: роль-модель как есть).</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>Обнаружено, не исправлено</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>Обнаружено при Ф2 редизайна, сессия 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>Баг</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Баги</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>TodayCards падает при ошибке API (нет проверки r.ok)</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>src/components/dashboard/today-cards.tsx:59 — fetch(...).then(r =&gt; r.json()) без проверки r.ok; если API вернёт {error: ...}, stats.orders.toLocaleString() упадёт (тот же паттерн, что был в самом dashboard/page.tsx, там уже исправлено). Не трогал — компонент вне рамок Ф2 (легаси-стиль, редизайн в след. фазах).</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>Обнаружено, не исправлено</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>Низкий</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>Обнаружено при тестировании Ф2, сессия 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="6" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" s="6" t="inlineStr">
+        <is>
+          <t>Идея</t>
+        </is>
+      </c>
+      <c r="C141" s="6" t="inlineStr">
+        <is>
+          <t>Редизайн — Steep</t>
+        </is>
+      </c>
+      <c r="D141" s="6" t="inlineStr">
+        <is>
+          <t>Полная консолидация навигации в 5 разделов (рейл-вкладки)</t>
+        </is>
+      </c>
+      <c r="E141" s="6" t="inlineStr">
+        <is>
+          <t>Сознательно не сделано в Ф4: объединить ~20 текущих страниц сайдбара в 5 разделов (Финансы: pnl+costs+cashflow+unit-economics+reports; Товары: abc+products+sku+storage+supplies+rnp+matrix и т.д.) с рейлом-вкладками между вложенными страницами внутри раздела и переделкой сайдбара/URL-структуры. Риск: затрагивает навигацию всего приложения. Делать отдельным, специально согласованным этапом. | Связано с Ф6 — если делать полную консолидацию, Ф6 (визуальное оформление оставшихся страниц) логично делать в рамках неё, а не до.</t>
+        </is>
+      </c>
+      <c r="F141" s="6" t="inlineStr">
+        <is>
+          <t>Не начато, требует отдельного решения</t>
+        </is>
+      </c>
+      <c r="G141" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H141" s="6" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="I141" s="6" t="inlineStr">
+        <is>
+          <t>Выделено из Ф4, сессия 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>Баг</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Баги</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Косметическое React dev-warning от anti-FOUC script в layout.tsx</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>src/app/layout.tsx — сырой &lt;script dangerouslySetInnerHTML&gt; для anti-FOUC применения тёмной темы триггерит консольное предупреждение React 19 "Encountered a script tag while rendering React component" на каждой загрузке (dev-режим). Функционально не мешает (тема работает и переживает reload), пробовал next/script beforeInteractive — не сработал надёжно (см. ту же строку выше). Можно оставить как есть (стандартный паттерн shadcn/next-themes) или заменить на полноценный next-themes пакет позже.</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>Известное ограничение, не исправлено</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>Низкий</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>Обнаружено при Ф5, сессия 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="4" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" s="4" t="inlineStr">
+        <is>
+          <t>Задача</t>
+        </is>
+      </c>
+      <c r="C143" s="4" t="inlineStr">
+        <is>
+          <t>Редизайн — Steep</t>
+        </is>
+      </c>
+      <c r="D143" s="4" t="inlineStr">
+        <is>
+          <t>Ф6 — Остальные страницы в Steep-стиле</t>
+        </is>
+      </c>
+      <c r="E143" s="4" t="inlineStr">
+        <is>
+          <t>Steep-оформление (eyebrow+serif заголовок, pill-период, SectionShell) сейчас применено только на 5 из ~20 страниц: Обзор (/dashboard), P&amp;L, Воронка, ABC, Реклама. Осталось: Товары/products, SKU, Хранение (/storage), Поставки (/supplies), РНП (/rnp), дк-Матрица, Затраты (/costs), Cash Flow, Юнитка (/unit-economics), Отчёты (/reports), Возвраты (/returns), План продаж (/sales-plan), Задачи (/tasks), Импорт (/import), Настройки (/settings), Логистика (/logistics), Качество (/quality). Плюс на самой /dashboard ниже разделителя «Разобрать детали» — блоки TodayCards/TopProducts/TopTasks/InsightsRow/SalesChart всё ещё в старом стиле (легаси, явно оставлено на потом при реализации Ф2). Подход — тот же, что в Ф4: только внешний слой (заголовок/период/SectionShell), внутреннюю логику/таблицы/графики не трогать, каждую страницу тестировать в браузере по отдельности.</t>
+        </is>
+      </c>
+      <c r="F143" s="4" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="G143" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H143" s="4" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="I143" s="4" t="inlineStr">
+        <is>
+          <t>Обнаружено при подведении итогов Ф0-Ф5, сессия 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="4" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" s="4" t="inlineStr">
+        <is>
+          <t>Задача</t>
+        </is>
+      </c>
+      <c r="C144" s="4" t="inlineStr">
+        <is>
+          <t>Редизайн — Steep</t>
+        </is>
+      </c>
+      <c r="D144" s="4" t="inlineStr">
+        <is>
+          <t>Ф7 — Адаптивность (планшет 768-1199px)</t>
+        </is>
+      </c>
+      <c r="E144" s="4" t="inlineStr">
+        <is>
+          <t>ТЗ §1 (DoD) явно требует адаптивность десктоп (≥1200) и планшет (768-1199) для всех редизайненных экранов — ни разу не проверялось за Ф0-Ф5. Нужно: preview_resize на все тронутые страницы (Обзор, P&amp;L, Воронка, ABC, Реклама + все компоненты Ф0-Ф5 — GlobalStatusBar, VerdictBand, SignalCard, ChartCard, 5 диаграмм, MetricGraph, SectionShell) на ширине планшета, найти и поправить переполнения/поломки сеток (grid-cols сейчас в основном md:grid-cols-2 — не проверено на границе 768px). Мобильная версия (&lt;768px) — явно вне рамок по ТЗ §11, трогать не нужно.</t>
+        </is>
+      </c>
+      <c r="F144" s="4" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="G144" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H144" s="4" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="I144" s="4" t="inlineStr">
+        <is>
+          <t>Обнаружено при подведении итогов Ф0-Ф5, сессия 2026-07-02</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I124"/>
+  <autoFilter ref="A1:I144"/>
   <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
 </file>
--- a/WB_Analytics_Реестр_задач.xlsx
+++ b/WB_Analytics_Реестр_задач.xlsx
@@ -6798,17 +6798,17 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>src/components/dashboard/today-cards.tsx:59 — fetch(...).then(r =&gt; r.json()) без проверки r.ok; если API вернёт {error: ...}, stats.orders.toLocaleString() упадёт (тот же паттерн, что был в самом dashboard/page.tsx, там уже исправлено). Не трогал — компонент вне рамок Ф2 (легаси-стиль, редизайн в след. фазах).</t>
+          <t>src/components/dashboard/today-cards.tsx:59 — fetch(...).then(r =&gt; r.json()) без проверки r.ok; если API вернёт {error: ...}, stats.orders.toLocaleString() упадёт (тот же паттерн, что был в самом dashboard/page.tsx, там уже исправлено). Не трогал — компонент вне рамок Ф2 (легаси-стиль, редизайн в след. фазах). | ИТОГ: добавлена проверка r.ok перед r.json() — при ошибке API (например {error: No stores}) карточки показывают '—' вместо краша stats.orders.toLocaleString(). Ветка feature/dev-bugfix-139-141.</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>Обнаружено, не исправлено</t>
+          <t>Исправлено (2026-07-03)</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -6888,17 +6888,17 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>src/app/layout.tsx — сырой &lt;script dangerouslySetInnerHTML&gt; для anti-FOUC применения тёмной темы триггерит консольное предупреждение React 19 "Encountered a script tag while rendering React component" на каждой загрузке (dev-режим). Функционально не мешает (тема работает и переживает reload), пробовал next/script beforeInteractive — не сработал надёжно (см. ту же строку выше). Можно оставить как есть (стандартный паттерн shadcn/next-themes) или заменить на полноценный next-themes пакет позже.</t>
+          <t>src/app/layout.tsx — сырой &lt;script dangerouslySetInnerHTML&gt; для anti-FOUC применения тёмной темы триггерит консольное предупреждение React 19 "Encountered a script tag while rendering React component" на каждой загрузке (dev-режим). Функционально не мешает (тема работает и переживает reload), пробовал next/script beforeInteractive — не сработал надёжно (см. ту же строку выше). Можно оставить как есть (стандартный паттерн shadcn/next-themes) или заменить на полноценный next-themes пакет позже. | ИТОГ: попытка переоспроизвести тремя способами (reload, Fast Refresh правкой layout.tsx, полная жёсткая навигация) — предупреждение ни разу не появилось. Вероятно разовый артефакт активного редактирования во время Ф5 в прошлой сессии. Решено не делать архитектурный рефактор (cookie-based theme, убирающий &lt;script&gt; из дерева) ради непроверяемого предупреждения — закрыто без изменений кода.</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>Известное ограничение, не исправлено</t>
+          <t>Закрыто — не воспроизводится (2026-07-03)</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">

--- a/WB_Analytics_Реестр_задач.xlsx
+++ b/WB_Analytics_Реестр_задач.xlsx
@@ -2703,17 +2703,17 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Поле subject (категория товара) не передаётся в wb_weekly_report_rows, поэтому fallback-путь определения срока фиксации (по разнице дат) не может определить категорию и всегда использует 90 дней вместо 60 для не-одежды. Приоритетный путь (fix_end_date из отчёта) работает корректно.</t>
+          <t>Поле subject (категория товара) не передаётся в wb_weekly_report_rows, поэтому fallback-путь определения срока фиксации (по разнице дат) не может определить категорию и всегда использует 90 дней вместо 60 для не-одежды. Приоритетный путь (fix_end_date из отчёта) работает корректно. | ИТОГ: исходная посылка бага была неверна — subject фактически ЕСТЬ в products.subject_id, просто не использовался. Родительская категория берётся из wb_commissions.parent_name (уже синхронизируется вместе с комиссиями WB). Методология подтверждена по п.6.6.3 Оферты товарной WB: 90 дней — одежда/обувь/спортивная одежда/головные уборы/одежда,бельё,аксессуары для малышей; 60 дней — все прочие. Добавлен join products.subject_id -&gt; wb_commissions.parent_name и константа FIXATION_90_DAY_PARENT_CATEGORIES в src/app/api/logistics/check/route.ts. На текущих данных магазина видимых цифр не меняет (все fallback-строки — одежда), но защищает от ошибки для будущих не-одёжных категорий. Ветка feature/dev-logistics-fixation-period.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Известное некритичное ограничение</t>
+          <t>Исправлено (2026-07-03)</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
